--- a/Mikhail_5_Sezonov_Raspisanie.xlsx
+++ b/Mikhail_5_Sezonov_Raspisanie.xlsx
@@ -12,7 +12,7 @@
     <sheet name="2014-2015 ПРЕМЬЕР-ЛИГА 7×7" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2014-2015 ВЫСШАЯ ЛИГА 7×7" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2016-2017 ПРЕМЬЕР-ЛИГА 7×7" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2016-2017 ВЫСШАЯ ЛИГА 5×5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 Г" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2018-2019 ПРЕМЬЕР-ЛИГА 5×5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2018-2019 ВЫСШАЯ ЛИГА 5×5" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2020-2021 • 13 команд" sheetId="9" state="visible" r:id="rId9"/>
@@ -31,9 +31,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$A$21:$H$175</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$1:$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$A$1:$H$177</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2016-2017 ВЫСШАЯ ЛИГА 5×5'!$A$28:$H$218</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2016-2017 ВЫСШАЯ ЛИГА 5×5'!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'2016-2017 ВЫСШАЯ ЛИГА 5×5'!$A$1:$H$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 Г'!$A$36:$H$102</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 Г'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 Г'!$A$1:$H$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$A$17:$H$87</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$1:$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$A$1:$H$89</definedName>
@@ -51,7 +51,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -201,8 +201,27 @@
       <color rgb="0064748B"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00475569"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -251,6 +270,36 @@
         <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D4ED8"/>
+        <bgColor rgb="001D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C2D12"/>
+        <bgColor rgb="007C2D12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006D28D9"/>
+        <bgColor rgb="006D28D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -278,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -395,6 +444,72 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -913,7 +1028,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2016-2017 ВЫСШАЯ ЛИГА 5×5</t>
+          <t>2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 ГРУПП × 4</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -922,10 +1037,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>171</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -27486,7 +27601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27495,28 +27610,28 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>2016-2017 ВЫСШАЯ ЛИГА 5×5</t>
+          <t>2016-2017 ВЫСШАЯ ЛИГА 5×5 — 5 ГРУПП × 4</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Сезон 2016-2017  •  Формат 5×5  •  ОДИН КРУГ  •  Старт: 2016-09-04  •  16:00  •  Манеж 5×5  •  19 команд</t>
+          <t>Сезон 2016-2017  •  Формат 5×5  •  ОДИН КРУГ  •  5 ГРУПП × 4 КОМАНДЫ  •  Старт: 2016-09-04  •  16:00  •  Манеж 5×5  •  20 команд</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Всего туров: 19  •  Всего матчей: 171  •  Формула: каждый с каждым  •  Сгенерировано автоматически</t>
+          <t>Групповой этап: 5 групп по 4 команды  •  В каждой группе каждый с каждым (3 тура, 6 матчей)  •  Всего матчей: 30  •  Далее плей-офф по желанию</t>
         </is>
       </c>
     </row>
@@ -28029,7196 +28144,2179 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>2. РАСПИСАНИЕ МАТЧЕЙ — КРУГОВАЯ СИСТЕМА (каждый с каждым)</t>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Эверест 3 (резерв)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Пузырев</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>☐</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2. ГРУППОВОЙ ЭТАП — 5 ГРУПП ПО 4 КОМАНДЫ (каждая группа — круговая)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>ГРУППА A — 4 команды: Эверест 2, Школа 64/92, Школа 139, Профики</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Эверест 2</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Пузырев</t>
+        </is>
+      </c>
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E31" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="C32" s="48" t="inlineStr">
+        <is>
+          <t>Тетерин</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>Гурин</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E33" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа A — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Тур</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>Время</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>Хозяева</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>Гости</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>Стадион</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>Счёт</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 1  —  04.09.2016</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="34" t="n">
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B37" s="51" t="inlineStr">
         <is>
           <t>04.09.2016</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C37" s="51" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="D37" s="52" t="inlineStr">
+        <is>
+          <t>Эверест 2</t>
+        </is>
+      </c>
+      <c r="E37" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G37" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H37" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="47" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="G38" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H38" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="51" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C39" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="E39" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>Эверест 2</t>
+        </is>
+      </c>
+      <c r="G39" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H39" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="47" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G40" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>Эверест 2</t>
+        </is>
+      </c>
+      <c r="E41" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G41" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H41" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="47" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G42" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H42" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="59" t="inlineStr">
+        <is>
+          <t>ГРУППА B — 4 команды: Профики-2, школа 16, КС 26, Комета</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Профики-2</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="47" t="inlineStr">
+        <is>
+          <t>школа 16</t>
+        </is>
+      </c>
+      <c r="C47" s="48" t="inlineStr">
+        <is>
+          <t>Смолкин</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+      <c r="D48" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="C49" s="48" t="inlineStr">
+        <is>
+          <t>Женя</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа B — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="55" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C52" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D52" s="56" t="inlineStr">
+        <is>
+          <t>Профики-2</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="47" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="G52" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H52" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D53" s="52" t="inlineStr">
+        <is>
+          <t>школа 16</t>
+        </is>
+      </c>
+      <c r="E53" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="43" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G53" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H53" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="55" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D54" s="56" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="47" t="inlineStr">
+        <is>
+          <t>Профики-2</t>
+        </is>
+      </c>
+      <c r="G54" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H54" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="51" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C55" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D55" s="52" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="43" t="inlineStr">
+        <is>
+          <t>школа 16</t>
+        </is>
+      </c>
+      <c r="G55" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H55" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" s="55" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C56" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D56" s="56" t="inlineStr">
+        <is>
+          <t>Профики-2</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="47" t="inlineStr">
+        <is>
+          <t>школа 16</t>
+        </is>
+      </c>
+      <c r="G56" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H56" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="51" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C57" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D57" s="52" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E57" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="43" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="G57" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H57" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="60" t="inlineStr">
+        <is>
+          <t>ГРУППА C — 4 команды: Молот, Школа 1, Школа 1/2, Барсы</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>Цыганов</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" s="43" t="inlineStr">
+        <is>
+          <t>Школа 1/2</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>Владимиров</t>
+        </is>
+      </c>
+      <c r="D63" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E63" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" s="47" t="inlineStr">
+        <is>
+          <t>Барсы</t>
+        </is>
+      </c>
+      <c r="C64" s="48" t="inlineStr">
+        <is>
+          <t>Седин</t>
+        </is>
+      </c>
+      <c r="D64" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E64" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа C — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D67" s="52" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="E67" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="43" t="inlineStr">
+        <is>
+          <t>Барсы</t>
+        </is>
+      </c>
+      <c r="G67" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H67" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" s="55" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C68" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D68" s="56" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E68" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="47" t="inlineStr">
+        <is>
+          <t>Школа 1/2</t>
+        </is>
+      </c>
+      <c r="G68" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H68" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D69" s="52" t="inlineStr">
+        <is>
+          <t>Школа 1/2</t>
+        </is>
+      </c>
+      <c r="E69" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="G69" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H69" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="55" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D70" s="56" t="inlineStr">
+        <is>
+          <t>Барсы</t>
+        </is>
+      </c>
+      <c r="E70" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="47" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G70" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H70" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="51" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C71" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D71" s="52" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="E71" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="43" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G71" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H71" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="55" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C72" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D72" s="56" t="inlineStr">
+        <is>
+          <t>Школа 1/2</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="47" t="inlineStr">
+        <is>
+          <t>Барсы</t>
+        </is>
+      </c>
+      <c r="G72" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H72" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="61" t="inlineStr">
+        <is>
+          <t>ГРУППА D — 4 команды: Красная фурия 2, Олимп 2, Огонь 2, Огонь 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="43" t="inlineStr">
+        <is>
+          <t>Красная фурия 2</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="inlineStr">
+        <is>
+          <t>Касьянов</t>
+        </is>
+      </c>
+      <c r="D76" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E76" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" s="47" t="inlineStr">
+        <is>
+          <t>Олимп 2</t>
+        </is>
+      </c>
+      <c r="C77" s="48" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="D77" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>Огонь 2</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D78" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E78" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" s="47" t="inlineStr">
+        <is>
+          <t>Огонь 3</t>
+        </is>
+      </c>
+      <c r="C79" s="48" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D79" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E79" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа D — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" s="55" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C82" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D82" s="56" t="inlineStr">
+        <is>
+          <t>Красная фурия 2</t>
+        </is>
+      </c>
+      <c r="E82" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="47" t="inlineStr">
+        <is>
+          <t>Огонь 3</t>
+        </is>
+      </c>
+      <c r="G82" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H82" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D83" s="52" t="inlineStr">
+        <is>
+          <t>Олимп 2</t>
+        </is>
+      </c>
+      <c r="E83" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="43" t="inlineStr">
+        <is>
+          <t>Огонь 2</t>
+        </is>
+      </c>
+      <c r="G83" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H83" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" s="55" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D84" s="56" t="inlineStr">
+        <is>
+          <t>Огонь 2</t>
+        </is>
+      </c>
+      <c r="E84" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="47" t="inlineStr">
+        <is>
+          <t>Красная фурия 2</t>
+        </is>
+      </c>
+      <c r="G84" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H84" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D85" s="52" t="inlineStr">
+        <is>
+          <t>Огонь 3</t>
+        </is>
+      </c>
+      <c r="E85" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="43" t="inlineStr">
+        <is>
+          <t>Олимп 2</t>
+        </is>
+      </c>
+      <c r="G85" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H85" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" s="55" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D86" s="56" t="inlineStr">
+        <is>
+          <t>Красная фурия 2</t>
+        </is>
+      </c>
+      <c r="E86" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="47" t="inlineStr">
+        <is>
+          <t>Олимп 2</t>
+        </is>
+      </c>
+      <c r="G86" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H86" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D87" s="52" t="inlineStr">
+        <is>
+          <t>Огонь 2</t>
+        </is>
+      </c>
+      <c r="E87" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="43" t="inlineStr">
+        <is>
+          <t>Огонь 3</t>
+        </is>
+      </c>
+      <c r="G87" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа D)</t>
+        </is>
+      </c>
+      <c r="H87" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="62" t="inlineStr">
+        <is>
+          <t>ГРУППА E — 4 команды: Огонь 4, Огонь 5, Дружба, Эверест 3 (резерв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" s="43" t="inlineStr">
+        <is>
+          <t>Огонь 4</t>
+        </is>
+      </c>
+      <c r="C91" s="44" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D91" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E91" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="47" t="inlineStr">
+        <is>
+          <t>Огонь 5</t>
+        </is>
+      </c>
+      <c r="C92" s="48" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D92" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E92" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G30" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H30" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="n">
+      <c r="C93" s="44" t="inlineStr">
+        <is>
+          <t>Майоров</t>
+        </is>
+      </c>
+      <c r="D93" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E93" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" s="47" t="inlineStr">
+        <is>
+          <t>Эверест 3 (резерв)</t>
+        </is>
+      </c>
+      <c r="C94" s="48" t="inlineStr">
+        <is>
+          <t>Пузырев</t>
+        </is>
+      </c>
+      <c r="D94" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E94" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа E — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B97" s="51" t="inlineStr">
         <is>
           <t>04.09.2016</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C97" s="51" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="D97" s="52" t="inlineStr">
+        <is>
+          <t>Огонь 4</t>
+        </is>
+      </c>
+      <c r="E97" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="43" t="inlineStr">
+        <is>
+          <t>Эверест 3 (резерв)</t>
+        </is>
+      </c>
+      <c r="G97" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H97" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="55" t="inlineStr">
+        <is>
+          <t>04.09.2016</t>
+        </is>
+      </c>
+      <c r="C98" s="55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D98" s="56" t="inlineStr">
         <is>
           <t>Огонь 5</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H31" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="E98" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="47" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="G98" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H98" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E32" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="D99" s="52" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E99" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="43" t="inlineStr">
         <is>
           <t>Огонь 4</t>
         </is>
       </c>
-      <c r="G32" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H32" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="G99" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H99" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B100" s="55" t="inlineStr">
+        <is>
+          <t>11.09.2016</t>
+        </is>
+      </c>
+      <c r="C100" s="55" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G33" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H33" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="D100" s="56" t="inlineStr">
+        <is>
+          <t>Эверест 3 (резерв)</t>
+        </is>
+      </c>
+      <c r="E100" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="47" t="inlineStr">
+        <is>
+          <t>Огонь 5</t>
+        </is>
+      </c>
+      <c r="G100" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H100" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G34" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H34" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="D101" s="52" t="inlineStr">
+        <is>
+          <t>Огонь 4</t>
+        </is>
+      </c>
+      <c r="E101" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="43" t="inlineStr">
+        <is>
+          <t>Огонь 5</t>
+        </is>
+      </c>
+      <c r="G101" s="53" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H101" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="55" t="inlineStr">
+        <is>
+          <t>18.09.2016</t>
+        </is>
+      </c>
+      <c r="C102" s="55" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G35" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H35" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D36" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E36" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G36" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H36" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D37" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H37" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>04.09.2016</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D38" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E38" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G38" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H38" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 2  —  11.09.2016</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="D102" s="56" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="E40" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G40" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H40" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G41" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H41" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D42" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E42" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G42" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H42" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G43" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H43" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D44" s="36" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E44" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G44" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H44" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E45" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G45" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H45" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D46" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E46" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G46" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H46" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G47" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H47" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>11.09.2016</t>
-        </is>
-      </c>
-      <c r="C48" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D48" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E48" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G48" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H48" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 3  —  18.09.2016</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C50" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D50" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E50" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G50" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H50" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G51" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H51" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="35" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C52" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D52" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E52" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G52" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H52" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B53" s="29" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G53" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H53" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="35" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C54" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E54" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G54" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H54" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E55" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G55" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H55" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C56" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E56" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G56" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H56" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="29" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C57" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E57" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G57" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H57" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>18.09.2016</t>
-        </is>
-      </c>
-      <c r="C58" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D58" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E58" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G58" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H58" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 4  —  25.09.2016</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="n"/>
-      <c r="C59" s="27" t="n"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
-      <c r="H59" s="27" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C60" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D60" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E60" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G60" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H60" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B61" s="29" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D61" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G61" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H61" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B62" s="35" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C62" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D62" s="36" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E62" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G62" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H62" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C63" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D63" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G63" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B64" s="35" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C64" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D64" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E64" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G64" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H64" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D65" s="30" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G65" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H65" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B66" s="35" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C66" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D66" s="36" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E66" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G66" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H66" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B67" s="29" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C67" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D67" s="30" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E67" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B68" s="35" t="inlineStr">
-        <is>
-          <t>25.09.2016</t>
-        </is>
-      </c>
-      <c r="C68" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D68" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G68" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H68" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 5  —  02.10.2016</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="n"/>
-      <c r="C69" s="27" t="n"/>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="27" t="n"/>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D70" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E70" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G70" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H70" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D71" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B72" s="35" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C72" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D72" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E72" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G72" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H72" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B73" s="29" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D73" s="30" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B74" s="35" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C74" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D74" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E74" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G74" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H74" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B75" s="29" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D75" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B76" s="35" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C76" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D76" s="36" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E76" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G76" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H76" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B78" s="35" t="inlineStr">
-        <is>
-          <t>02.10.2016</t>
-        </is>
-      </c>
-      <c r="C78" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D78" s="36" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G78" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H78" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 6  —  09.10.2016</t>
-        </is>
-      </c>
-      <c r="B79" s="27" t="n"/>
-      <c r="C79" s="27" t="n"/>
-      <c r="D79" s="27" t="n"/>
-      <c r="E79" s="27" t="n"/>
-      <c r="F79" s="27" t="n"/>
-      <c r="G79" s="27" t="n"/>
-      <c r="H79" s="27" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="35" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C80" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D80" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G80" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H80" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="29" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C81" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D81" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="35" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C82" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D82" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E82" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G82" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H82" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B83" s="29" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C83" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D83" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G83" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="35" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C84" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D84" s="36" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E84" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G84" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H84" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="29" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C85" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D85" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E85" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G85" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H85" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B86" s="35" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C86" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D86" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E86" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G86" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H86" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B87" s="29" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D87" s="30" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E87" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G87" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H87" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B88" s="35" t="inlineStr">
-        <is>
-          <t>09.10.2016</t>
-        </is>
-      </c>
-      <c r="C88" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D88" s="36" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G88" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H88" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 7  —  16.10.2016</t>
-        </is>
-      </c>
-      <c r="B89" s="27" t="n"/>
-      <c r="C89" s="27" t="n"/>
-      <c r="D89" s="27" t="n"/>
-      <c r="E89" s="27" t="n"/>
-      <c r="F89" s="27" t="n"/>
-      <c r="G89" s="27" t="n"/>
-      <c r="H89" s="27" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B90" s="35" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C90" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D90" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E90" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G90" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H90" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B91" s="29" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C91" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D91" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E91" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G91" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H91" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B92" s="35" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C92" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D92" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E92" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G92" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H92" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B93" s="29" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C93" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D93" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E93" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G93" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H93" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B94" s="35" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C94" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D94" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E94" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G94" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H94" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B95" s="29" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C95" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D95" s="30" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E95" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G95" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H95" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B96" s="35" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C96" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D96" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E96" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G96" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H96" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B97" s="29" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C97" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D97" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E97" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G97" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H97" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B98" s="35" t="inlineStr">
-        <is>
-          <t>16.10.2016</t>
-        </is>
-      </c>
-      <c r="C98" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D98" s="36" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E98" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G98" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H98" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 8  —  23.10.2016</t>
-        </is>
-      </c>
-      <c r="B99" s="27" t="n"/>
-      <c r="C99" s="27" t="n"/>
-      <c r="D99" s="27" t="n"/>
-      <c r="E99" s="27" t="n"/>
-      <c r="F99" s="27" t="n"/>
-      <c r="G99" s="27" t="n"/>
-      <c r="H99" s="27" t="n"/>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B100" s="35" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C100" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D100" s="36" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E100" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G100" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H100" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B101" s="29" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C101" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D101" s="30" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E101" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G101" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H101" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B102" s="35" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C102" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D102" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E102" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G102" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H102" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B103" s="29" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C103" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D103" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E103" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G103" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H103" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B104" s="35" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C104" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D104" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E104" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G104" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H104" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B105" s="29" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C105" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D105" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E105" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G105" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H105" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B106" s="35" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C106" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D106" s="36" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E106" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G106" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H106" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B107" s="29" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C107" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D107" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E107" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G107" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H107" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B108" s="35" t="inlineStr">
-        <is>
-          <t>23.10.2016</t>
-        </is>
-      </c>
-      <c r="C108" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D108" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E108" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G108" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H108" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 9  —  30.10.2016</t>
-        </is>
-      </c>
-      <c r="B109" s="27" t="n"/>
-      <c r="C109" s="27" t="n"/>
-      <c r="D109" s="27" t="n"/>
-      <c r="E109" s="27" t="n"/>
-      <c r="F109" s="27" t="n"/>
-      <c r="G109" s="27" t="n"/>
-      <c r="H109" s="27" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B110" s="35" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C110" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D110" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E110" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G110" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H110" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B111" s="29" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C111" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D111" s="30" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E111" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="G111" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H111" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B112" s="35" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C112" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D112" s="36" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E112" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G112" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H112" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B113" s="29" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C113" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D113" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E113" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G113" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H113" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B114" s="35" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C114" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D114" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E114" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G114" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H114" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B115" s="29" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C115" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D115" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E115" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G115" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H115" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B116" s="35" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C116" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D116" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E116" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G116" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H116" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B117" s="29" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C117" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D117" s="30" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E117" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G117" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H117" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B118" s="35" t="inlineStr">
-        <is>
-          <t>30.10.2016</t>
-        </is>
-      </c>
-      <c r="C118" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D118" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E118" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G118" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H118" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 10  —  06.11.2016</t>
-        </is>
-      </c>
-      <c r="B119" s="27" t="n"/>
-      <c r="C119" s="27" t="n"/>
-      <c r="D119" s="27" t="n"/>
-      <c r="E119" s="27" t="n"/>
-      <c r="F119" s="27" t="n"/>
-      <c r="G119" s="27" t="n"/>
-      <c r="H119" s="27" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B120" s="35" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C120" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D120" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E120" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G120" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H120" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B121" s="29" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C121" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D121" s="30" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E121" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G121" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H121" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B122" s="35" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C122" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D122" s="36" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E122" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G122" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H122" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B123" s="29" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C123" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D123" s="30" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E123" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G123" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H123" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B124" s="35" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C124" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D124" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E124" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G124" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H124" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B125" s="29" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C125" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D125" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E125" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G125" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H125" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B126" s="35" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C126" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D126" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E126" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G126" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H126" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B127" s="29" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C127" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D127" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E127" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G127" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H127" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B128" s="35" t="inlineStr">
-        <is>
-          <t>06.11.2016</t>
-        </is>
-      </c>
-      <c r="C128" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D128" s="36" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="E128" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G128" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H128" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 11  —  13.11.2016</t>
-        </is>
-      </c>
-      <c r="B129" s="27" t="n"/>
-      <c r="C129" s="27" t="n"/>
-      <c r="D129" s="27" t="n"/>
-      <c r="E129" s="27" t="n"/>
-      <c r="F129" s="27" t="n"/>
-      <c r="G129" s="27" t="n"/>
-      <c r="H129" s="27" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B130" s="35" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C130" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D130" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E130" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="G130" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H130" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B131" s="29" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C131" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D131" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E131" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G131" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H131" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B132" s="35" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C132" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D132" s="36" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E132" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G132" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H132" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B133" s="29" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C133" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D133" s="30" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E133" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G133" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H133" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B134" s="35" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C134" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D134" s="36" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E134" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G134" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H134" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B135" s="29" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C135" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D135" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E135" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G135" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H135" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B136" s="35" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C136" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D136" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E136" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G136" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H136" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B137" s="29" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C137" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D137" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E137" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G137" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H137" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B138" s="35" t="inlineStr">
-        <is>
-          <t>13.11.2016</t>
-        </is>
-      </c>
-      <c r="C138" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D138" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E138" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G138" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H138" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 12  —  20.11.2016</t>
-        </is>
-      </c>
-      <c r="B139" s="27" t="n"/>
-      <c r="C139" s="27" t="n"/>
-      <c r="D139" s="27" t="n"/>
-      <c r="E139" s="27" t="n"/>
-      <c r="F139" s="27" t="n"/>
-      <c r="G139" s="27" t="n"/>
-      <c r="H139" s="27" t="n"/>
-    </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B140" s="35" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C140" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D140" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E140" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G140" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H140" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B141" s="29" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C141" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D141" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E141" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G141" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H141" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B142" s="35" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C142" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D142" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E142" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G142" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H142" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B143" s="29" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C143" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D143" s="30" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E143" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G143" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H143" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B144" s="35" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C144" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D144" s="36" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E144" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G144" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H144" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B145" s="29" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C145" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D145" s="30" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E145" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G145" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H145" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B146" s="35" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C146" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D146" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E146" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G146" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H146" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B147" s="29" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C147" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D147" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E147" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G147" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H147" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B148" s="35" t="inlineStr">
-        <is>
-          <t>20.11.2016</t>
-        </is>
-      </c>
-      <c r="C148" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D148" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="E148" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G148" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H148" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 13  —  27.11.2016</t>
-        </is>
-      </c>
-      <c r="B149" s="27" t="n"/>
-      <c r="C149" s="27" t="n"/>
-      <c r="D149" s="27" t="n"/>
-      <c r="E149" s="27" t="n"/>
-      <c r="F149" s="27" t="n"/>
-      <c r="G149" s="27" t="n"/>
-      <c r="H149" s="27" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B150" s="35" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C150" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D150" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E150" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G150" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H150" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B151" s="29" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C151" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D151" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E151" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G151" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H151" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B152" s="35" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C152" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D152" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E152" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G152" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H152" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B153" s="29" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C153" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D153" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E153" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G153" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H153" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B154" s="35" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C154" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D154" s="36" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E154" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G154" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H154" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B155" s="29" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C155" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D155" s="30" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E155" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G155" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H155" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B156" s="35" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C156" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D156" s="36" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E156" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G156" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H156" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B157" s="29" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C157" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D157" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E157" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G157" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H157" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B158" s="35" t="inlineStr">
-        <is>
-          <t>27.11.2016</t>
-        </is>
-      </c>
-      <c r="C158" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D158" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="E158" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G158" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H158" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 14  —  04.12.2016</t>
-        </is>
-      </c>
-      <c r="B159" s="27" t="n"/>
-      <c r="C159" s="27" t="n"/>
-      <c r="D159" s="27" t="n"/>
-      <c r="E159" s="27" t="n"/>
-      <c r="F159" s="27" t="n"/>
-      <c r="G159" s="27" t="n"/>
-      <c r="H159" s="27" t="n"/>
-    </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B160" s="35" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C160" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D160" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E160" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G160" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H160" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B161" s="29" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C161" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D161" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E161" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G161" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H161" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B162" s="35" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C162" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D162" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E162" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G162" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H162" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B163" s="29" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C163" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D163" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E163" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G163" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H163" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B164" s="35" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C164" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D164" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E164" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G164" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H164" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B165" s="29" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C165" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D165" s="30" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E165" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G165" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H165" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B166" s="35" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C166" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D166" s="36" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E166" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G166" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H166" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B167" s="29" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C167" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D167" s="30" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E167" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G167" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H167" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B168" s="35" t="inlineStr">
-        <is>
-          <t>04.12.2016</t>
-        </is>
-      </c>
-      <c r="C168" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D168" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="E168" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G168" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H168" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 15  —  11.12.2016</t>
-        </is>
-      </c>
-      <c r="B169" s="27" t="n"/>
-      <c r="C169" s="27" t="n"/>
-      <c r="D169" s="27" t="n"/>
-      <c r="E169" s="27" t="n"/>
-      <c r="F169" s="27" t="n"/>
-      <c r="G169" s="27" t="n"/>
-      <c r="H169" s="27" t="n"/>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B170" s="35" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C170" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D170" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E170" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="G170" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H170" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B171" s="29" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C171" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D171" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E171" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="G171" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H171" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B172" s="35" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C172" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D172" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E172" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G172" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H172" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B173" s="29" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C173" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D173" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E173" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G173" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H173" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B174" s="35" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C174" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D174" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E174" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G174" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H174" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B175" s="29" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C175" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D175" s="30" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E175" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G175" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H175" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="15" customHeight="1">
-      <c r="A176" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B176" s="35" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C176" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D176" s="36" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E176" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G176" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H176" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B177" s="29" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C177" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D177" s="30" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E177" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G177" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H177" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B178" s="35" t="inlineStr">
-        <is>
-          <t>11.12.2016</t>
-        </is>
-      </c>
-      <c r="C178" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D178" s="36" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="E178" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G178" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H178" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 16  —  18.12.2016</t>
-        </is>
-      </c>
-      <c r="B179" s="27" t="n"/>
-      <c r="C179" s="27" t="n"/>
-      <c r="D179" s="27" t="n"/>
-      <c r="E179" s="27" t="n"/>
-      <c r="F179" s="27" t="n"/>
-      <c r="G179" s="27" t="n"/>
-      <c r="H179" s="27" t="n"/>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B180" s="35" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C180" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D180" s="36" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E180" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F180" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G180" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H180" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B181" s="29" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C181" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D181" s="30" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E181" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G181" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H181" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B182" s="35" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C182" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D182" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E182" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G182" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H182" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B183" s="29" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C183" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D183" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E183" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G183" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H183" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B184" s="35" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C184" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D184" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E184" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G184" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H184" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B185" s="29" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C185" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D185" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E185" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G185" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H185" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B186" s="35" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C186" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D186" s="36" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E186" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G186" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H186" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="15" customHeight="1">
-      <c r="A187" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B187" s="29" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C187" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D187" s="30" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E187" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G187" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H187" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="15" customHeight="1">
-      <c r="A188" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B188" s="35" t="inlineStr">
-        <is>
-          <t>18.12.2016</t>
-        </is>
-      </c>
-      <c r="C188" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D188" s="36" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="E188" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F188" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G188" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H188" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 17  —  25.12.2016</t>
-        </is>
-      </c>
-      <c r="B189" s="27" t="n"/>
-      <c r="C189" s="27" t="n"/>
-      <c r="D189" s="27" t="n"/>
-      <c r="E189" s="27" t="n"/>
-      <c r="F189" s="27" t="n"/>
-      <c r="G189" s="27" t="n"/>
-      <c r="H189" s="27" t="n"/>
-    </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B190" s="35" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C190" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D190" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E190" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F190" s="9" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="G190" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H190" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B191" s="29" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C191" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D191" s="30" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E191" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G191" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H191" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B192" s="35" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C192" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D192" s="36" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E192" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F192" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G192" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H192" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B193" s="29" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C193" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D193" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E193" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G193" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H193" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B194" s="35" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C194" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D194" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E194" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F194" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G194" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H194" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B195" s="29" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C195" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D195" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E195" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G195" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H195" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B196" s="35" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C196" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D196" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E196" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G196" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H196" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="15" customHeight="1">
-      <c r="A197" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B197" s="29" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C197" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D197" s="30" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E197" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G197" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H197" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="15" customHeight="1">
-      <c r="A198" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B198" s="35" t="inlineStr">
-        <is>
-          <t>25.12.2016</t>
-        </is>
-      </c>
-      <c r="C198" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D198" s="36" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="E198" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F198" s="9" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G198" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H198" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 18  —  01.01.2017</t>
-        </is>
-      </c>
-      <c r="B199" s="27" t="n"/>
-      <c r="C199" s="27" t="n"/>
-      <c r="D199" s="27" t="n"/>
-      <c r="E199" s="27" t="n"/>
-      <c r="F199" s="27" t="n"/>
-      <c r="G199" s="27" t="n"/>
-      <c r="H199" s="27" t="n"/>
-    </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B200" s="35" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C200" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D200" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E200" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F200" s="9" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="G200" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H200" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B201" s="29" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C201" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D201" s="30" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E201" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G201" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H201" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="15" customHeight="1">
-      <c r="A202" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B202" s="35" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C202" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D202" s="36" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E202" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F202" s="9" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G202" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H202" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B203" s="29" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C203" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D203" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E203" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G203" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H203" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B204" s="35" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C204" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D204" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E204" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G204" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H204" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B205" s="29" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C205" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D205" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E205" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G205" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H205" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B206" s="35" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C206" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D206" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E206" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F206" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G206" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H206" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B207" s="29" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C207" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D207" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E207" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G207" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H207" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B208" s="35" t="inlineStr">
-        <is>
-          <t>01.01.2017</t>
-        </is>
-      </c>
-      <c r="C208" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D208" s="36" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="E208" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F208" s="9" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G208" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H208" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 19  —  08.01.2017</t>
-        </is>
-      </c>
-      <c r="B209" s="27" t="n"/>
-      <c r="C209" s="27" t="n"/>
-      <c r="D209" s="27" t="n"/>
-      <c r="E209" s="27" t="n"/>
-      <c r="F209" s="27" t="n"/>
-      <c r="G209" s="27" t="n"/>
-      <c r="H209" s="27" t="n"/>
-    </row>
-    <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B210" s="35" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C210" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D210" s="36" t="inlineStr">
-        <is>
-          <t>Эверест 2</t>
-        </is>
-      </c>
-      <c r="E210" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G210" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H210" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="B211" s="29" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C211" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D211" s="30" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="E211" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="G211" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H211" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B212" s="35" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C212" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D212" s="36" t="inlineStr">
-        <is>
-          <t>Профики-2</t>
-        </is>
-      </c>
-      <c r="E212" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 5</t>
-        </is>
-      </c>
-      <c r="G212" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H212" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="15" customHeight="1">
-      <c r="A213" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="B213" s="29" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C213" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D213" s="30" t="inlineStr">
-        <is>
-          <t>школа 16</t>
-        </is>
-      </c>
-      <c r="E213" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 4</t>
-        </is>
-      </c>
-      <c r="G213" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H213" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B214" s="35" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C214" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D214" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E214" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F214" s="9" t="inlineStr">
-        <is>
-          <t>Огонь 3</t>
-        </is>
-      </c>
-      <c r="G214" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H214" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="B215" s="29" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C215" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D215" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E215" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>Огонь 2</t>
-        </is>
-      </c>
-      <c r="G215" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H215" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="15" customHeight="1">
-      <c r="A216" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B216" s="35" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C216" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D216" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E216" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F216" s="9" t="inlineStr">
-        <is>
-          <t>Олимп 2</t>
-        </is>
-      </c>
-      <c r="G216" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H216" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="B217" s="29" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C217" s="29" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D217" s="30" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="E217" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>Красная фурия 2</t>
-        </is>
-      </c>
-      <c r="G217" s="32" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H217" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B218" s="35" t="inlineStr">
-        <is>
-          <t>08.01.2017</t>
-        </is>
-      </c>
-      <c r="C218" s="35" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D218" s="36" t="inlineStr">
-        <is>
-          <t>Школа 1/2</t>
-        </is>
-      </c>
-      <c r="E218" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>Барсы</t>
-        </is>
-      </c>
-      <c r="G218" s="38" t="inlineStr">
-        <is>
-          <t>Манеж 5×5</t>
-        </is>
-      </c>
-      <c r="H218" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="40" t="inlineStr">
-        <is>
-          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1). Для переноса матча меняй дату/время. Распечатай: Файл → Печать → Альбомная, вписать на 1 стр.</t>
+      <c r="E102" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="47" t="inlineStr">
+        <is>
+          <t>Эверест 3 (резерв)</t>
+        </is>
+      </c>
+      <c r="G102" s="57" t="inlineStr">
+        <is>
+          <t>Манеж 5×5 (Группа E)</t>
+        </is>
+      </c>
+      <c r="H102" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="40" t="inlineStr">
+        <is>
+          <t>* В каждой группе — 3 тура, 6 матчей (один круг). Для выхода в плей-офф бери по 1-2 лучшие команды из каждой группы. Счёт вписывай в столбец «Счёт». Группу E можешь переименовать, резерв убери если не нужен.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A28:H218"/>
-  <mergeCells count="25">
-    <mergeCell ref="A39:H39"/>
+  <autoFilter ref="A36:H102"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A169:H169"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A119:H119"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A189:H189"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A149:H149"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A139:H139"/>
-    <mergeCell ref="A179:H179"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A159:H159"/>
-    <mergeCell ref="A209:H209"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A199:H199"/>
-    <mergeCell ref="A220:H220"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Mikhail_5_Sezonov_Raspisanie.xlsx
+++ b/Mikhail_5_Sezonov_Raspisanie.xlsx
@@ -25,9 +25,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014-2015 ПРЕМЬЕР-ЛИГА 7×7'!$A$17:$H$87</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2014-2015 ПРЕМЬЕР-ЛИГА 7×7'!$1:$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2014-2015 ПРЕМЬЕР-ЛИГА 7×7'!$A$1:$H$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2014-2015 ВЫСШАЯ ЛИГА 7×7'!$A$27:$H$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2014-2015 ВЫСШАЯ ЛИГА 7×7'!$A$36:$H$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2014-2015 ВЫСШАЯ ЛИГА 7×7'!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'2014-2015 ВЫСШАЯ ЛИГА 7×7'!$A$1:$H$199</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'2014-2015 ВЫСШАЯ ЛИГА 7×7'!$A$1:$H$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$A$21:$H$175</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$1:$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2016-2017 ПРЕМЬЕР-ЛИГА 7×7'!$A$1:$H$177</definedName>
@@ -994,7 +994,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>153</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -14576,7 +14576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14585,7 +14585,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -14599,14 +14599,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Сезон 2014-2015  •  Формат 7×7  •  ОДИН КРУГ  •  Старт: 2014-09-07  •  17:00  •  Поле №2  •  18 команд</t>
+          <t>Сезон 2014-2015  •  Формат 7×7  •  ОДИН КРУГ  •  5 ГРУПП × 4 КОМАНДЫ  •  Старт: 2014-09-07  •  17:00  •  Поле №2  •  18 команд</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Всего туров: 17  •  Всего матчей: 153  •  Формула: каждый с каждым  •  Сгенерировано автоматически</t>
+          <t>Групповой этап: 5 групп по 4 команды  •  В каждой группе каждый с каждым (3 тура, 6 матчей)  •  Всего матчей: 45  •  Далее плей-офф по желанию</t>
         </is>
       </c>
     </row>
@@ -15097,6443 +15097,2531 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>2. РАСПИСАНИЕ МАТЧЕЙ — КРУГОВАЯ СИСТЕМА (каждый с каждым)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+          <t>2. ГРУППОВОЙ ЭТАП — 5 ГРУПП ПО 4 КОМАНДЫ (каждая группа — круговая)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>ГРУППА A — 6 команды: 68 школа, Школа 175/96, Крылья дубль-школа №7, Школа 64/92, Смена КС (К), Школа 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E29" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>Лысиков</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Уразаков</t>
+        </is>
+      </c>
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E31" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="C32" s="48" t="inlineStr">
+        <is>
+          <t>Тетерин</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>Якимов</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E33" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>Гурин</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа A — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Тур</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>Время</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>Хозяева</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>Гости</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>Стадион</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>Счёт</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 1  —  07.09.2014</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="n">
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B37" s="51" t="inlineStr">
         <is>
           <t>07.09.2014</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C37" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D37" s="52" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E37" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="G37" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H37" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="47" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="G38" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H38" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="51" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C39" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="E39" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G39" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H39" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="47" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="G40" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="E41" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G41" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H41" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="47" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="G42" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H42" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D43" s="52" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G43" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H43" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="55" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C44" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="47" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="G44" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H44" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D45" s="52" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="G45" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H45" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="47" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="G46" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H46" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D47" s="52" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="G47" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H47" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C48" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D48" s="56" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="47" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="G48" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H48" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D49" s="52" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="43" t="inlineStr">
+        <is>
+          <t>Школа 175/96</t>
+        </is>
+      </c>
+      <c r="G49" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H49" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D50" s="56" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="G50" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H50" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="43" t="inlineStr">
+        <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="G51" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа A)</t>
+        </is>
+      </c>
+      <c r="H51" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="59" t="inlineStr">
+        <is>
+          <t>ГРУППА B — 6 команды: Школа 16, КС 26, Смена-Ведиси, Комета, Молот, Олимп</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>Смолкин</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="C56" s="48" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="43" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>Куликов</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E57" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" s="47" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>Женя</t>
+        </is>
+      </c>
+      <c r="D58" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Цыганов</t>
+        </is>
+      </c>
+      <c r="D59" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="C60" s="48" t="inlineStr">
+        <is>
+          <t>Седин</t>
+        </is>
+      </c>
+      <c r="D60" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E60" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа B — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D63" s="52" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E63" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="43" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="G63" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H63" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" s="55" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C64" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D64" s="56" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E64" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="47" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="G64" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H64" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C65" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D65" s="52" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="E65" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="43" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="G65" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H65" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D66" s="56" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="E66" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="47" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G66" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H66" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D67" s="52" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="E67" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="43" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="G67" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H67" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C68" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D68" s="56" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E68" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="47" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="G68" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H68" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D69" s="52" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E69" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="G69" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H69" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="55" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D70" s="56" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="E70" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="47" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="G70" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H70" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C71" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D71" s="52" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="E71" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="43" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G71" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H71" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C72" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D72" s="56" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="47" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G72" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H72" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="51" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C73" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D73" s="52" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="E73" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="43" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G73" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H73" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C74" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D74" s="56" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="E74" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="47" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="G74" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H74" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D75" s="52" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E75" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="43" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G75" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H75" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" s="55" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C76" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D76" s="56" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="E76" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="47" t="inlineStr">
+        <is>
+          <t>Олимп</t>
+        </is>
+      </c>
+      <c r="G76" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H76" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C77" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D77" s="52" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="E77" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="43" t="inlineStr">
+        <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="G77" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа B)</t>
+        </is>
+      </c>
+      <c r="H77" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="60" t="inlineStr">
+        <is>
+          <t>ГРУППА C — 6 команды: Школа 35, Галатасарай, Орлы 2, Орлы 3, Орлы 4, Орлы 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Взнос</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>Заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="C81" s="44" t="inlineStr">
+        <is>
+          <t>Колюжный</t>
+        </is>
+      </c>
+      <c r="D81" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E81" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" s="47" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="C82" s="48" t="inlineStr">
+        <is>
+          <t>Лысиков</t>
+        </is>
+      </c>
+      <c r="D82" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E82" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t>Орлы 2</t>
+        </is>
+      </c>
+      <c r="C83" s="44" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E83" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" s="47" t="inlineStr">
+        <is>
+          <t>Орлы 3</t>
+        </is>
+      </c>
+      <c r="C84" s="48" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D84" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E84" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B85" s="43" t="inlineStr">
+        <is>
+          <t>Орлы 4</t>
+        </is>
+      </c>
+      <c r="C85" s="44" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D85" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E85" s="45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B86" s="47" t="inlineStr">
         <is>
           <t>Орлы 5</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H29" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="34" t="n">
+      <c r="C86" s="48" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="D86" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E86" s="49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="50" t="inlineStr">
+        <is>
+          <t>Расписание Группа C — каждый с каждым</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>Тур</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>Стадион</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>Счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B89" s="51" t="inlineStr">
         <is>
           <t>07.09.2014</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C89" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E30" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="D89" s="52" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E89" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="43" t="inlineStr">
+        <is>
+          <t>Орлы 5</t>
+        </is>
+      </c>
+      <c r="G89" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H89" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" s="55" t="inlineStr">
+        <is>
+          <t>07.09.2014</t>
+        </is>
+      </c>
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D90" s="56" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="E90" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="47" t="inlineStr">
         <is>
           <t>Орлы 4</t>
         </is>
       </c>
-      <c r="G30" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H30" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="n">
+      <c r="G90" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H90" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B91" s="51" t="inlineStr">
         <is>
           <t>07.09.2014</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C91" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="D91" s="52" t="inlineStr">
+        <is>
+          <t>Орлы 2</t>
+        </is>
+      </c>
+      <c r="E91" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="43" t="inlineStr">
         <is>
           <t>Орлы 3</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H31" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="G91" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H91" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C92" s="55" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E32" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="D92" s="56" t="inlineStr">
+        <is>
+          <t>Орлы 4</t>
+        </is>
+      </c>
+      <c r="E92" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="47" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G92" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H92" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D93" s="52" t="inlineStr">
+        <is>
+          <t>Орлы 5</t>
+        </is>
+      </c>
+      <c r="E93" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="43" t="inlineStr">
+        <is>
+          <t>Орлы 3</t>
+        </is>
+      </c>
+      <c r="G93" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H93" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B94" s="55" t="inlineStr">
+        <is>
+          <t>14.09.2014</t>
+        </is>
+      </c>
+      <c r="C94" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D94" s="56" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="E94" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="47" t="inlineStr">
         <is>
           <t>Орлы 2</t>
         </is>
       </c>
-      <c r="G32" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H32" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="G94" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H94" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C95" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="D95" s="52" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E95" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="43" t="inlineStr">
+        <is>
+          <t>Орлы 3</t>
+        </is>
+      </c>
+      <c r="G95" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H95" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" s="55" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C96" s="55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D96" s="56" t="inlineStr">
+        <is>
+          <t>Орлы 4</t>
+        </is>
+      </c>
+      <c r="E96" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="47" t="inlineStr">
+        <is>
+          <t>Орлы 2</t>
+        </is>
+      </c>
+      <c r="G96" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H96" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>21.09.2014</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D97" s="52" t="inlineStr">
+        <is>
+          <t>Орлы 5</t>
+        </is>
+      </c>
+      <c r="E97" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="43" t="inlineStr">
         <is>
           <t>Галатасарай</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H33" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="G97" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H97" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C98" s="55" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="D98" s="56" t="inlineStr">
+        <is>
+          <t>Орлы 2</t>
+        </is>
+      </c>
+      <c r="E98" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="47" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="G34" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H34" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="G98" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H98" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G35" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H35" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="D99" s="52" t="inlineStr">
+        <is>
+          <t>Орлы 3</t>
+        </is>
+      </c>
+      <c r="E99" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="43" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="G99" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H99" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" s="55" t="inlineStr">
+        <is>
+          <t>28.09.2014</t>
+        </is>
+      </c>
+      <c r="C100" s="55" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E36" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G36" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H36" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>07.09.2014</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="D100" s="56" t="inlineStr">
+        <is>
+          <t>Орлы 4</t>
+        </is>
+      </c>
+      <c r="E100" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="47" t="inlineStr">
+        <is>
+          <t>Орлы 5</t>
+        </is>
+      </c>
+      <c r="G100" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H100" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H37" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 2  —  14.09.2014</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" s="29" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="D101" s="52" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E101" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="43" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="G101" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H101" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B102" s="55" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C102" s="55" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D102" s="56" t="inlineStr">
+        <is>
+          <t>Орлы 2</t>
+        </is>
+      </c>
+      <c r="E102" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="47" t="inlineStr">
+        <is>
+          <t>Орлы 5</t>
+        </is>
+      </c>
+      <c r="G102" s="57" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H102" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>05.10.2014</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D103" s="52" t="inlineStr">
+        <is>
+          <t>Орлы 3</t>
+        </is>
+      </c>
+      <c r="E103" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="43" t="inlineStr">
         <is>
           <t>Орлы 4</t>
         </is>
       </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G39" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H39" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D40" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E40" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G40" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H40" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G41" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H41" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D42" s="36" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E42" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G42" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H42" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G43" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H43" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D44" s="36" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E44" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G44" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H44" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E45" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G45" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H45" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D46" s="36" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E46" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G46" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H46" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>14.09.2014</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G47" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H47" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 3  —  21.09.2014</t>
-        </is>
-      </c>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
-      <c r="H48" s="27" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B49" s="29" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G49" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H49" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C50" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D50" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E50" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G50" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H50" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G51" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H51" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="35" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C52" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D52" s="36" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E52" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G52" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H52" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B53" s="29" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G53" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H53" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="35" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C54" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E54" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G54" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H54" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E55" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G55" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H55" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C56" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E56" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G56" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H56" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="29" t="inlineStr">
-        <is>
-          <t>21.09.2014</t>
-        </is>
-      </c>
-      <c r="C57" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E57" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G57" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H57" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 4  —  28.09.2014</t>
-        </is>
-      </c>
-      <c r="B58" s="27" t="n"/>
-      <c r="C58" s="27" t="n"/>
-      <c r="D58" s="27" t="n"/>
-      <c r="E58" s="27" t="n"/>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="27" t="n"/>
-      <c r="H58" s="27" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59" s="29" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C59" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D59" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G59" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H59" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C60" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D60" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E60" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G60" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H60" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B61" s="29" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D61" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G61" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H61" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B62" s="35" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C62" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D62" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E62" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G62" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H62" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C63" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D63" s="30" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G63" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B64" s="35" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C64" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D64" s="36" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E64" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G64" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H64" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D65" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G65" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H65" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B66" s="35" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C66" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D66" s="36" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E66" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G66" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H66" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B67" s="29" t="inlineStr">
-        <is>
-          <t>28.09.2014</t>
-        </is>
-      </c>
-      <c r="C67" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D67" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E67" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 5  —  05.10.2014</t>
-        </is>
-      </c>
-      <c r="B68" s="27" t="n"/>
-      <c r="C68" s="27" t="n"/>
-      <c r="D68" s="27" t="n"/>
-      <c r="E68" s="27" t="n"/>
-      <c r="F68" s="27" t="n"/>
-      <c r="G68" s="27" t="n"/>
-      <c r="H68" s="27" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D70" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E70" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G70" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H70" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D71" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B72" s="35" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C72" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D72" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E72" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G72" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H72" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B73" s="29" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D73" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B74" s="35" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C74" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D74" s="36" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E74" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G74" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H74" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B75" s="29" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D75" s="30" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B76" s="35" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C76" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D76" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E76" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G76" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H76" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>05.10.2014</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 6  —  12.10.2014</t>
-        </is>
-      </c>
-      <c r="B78" s="27" t="n"/>
-      <c r="C78" s="27" t="n"/>
-      <c r="D78" s="27" t="n"/>
-      <c r="E78" s="27" t="n"/>
-      <c r="F78" s="27" t="n"/>
-      <c r="G78" s="27" t="n"/>
-      <c r="H78" s="27" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="29" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D79" s="30" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="35" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C80" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D80" s="36" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G80" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H80" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="29" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C81" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D81" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="35" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C82" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D82" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E82" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G82" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H82" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B83" s="29" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C83" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D83" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G83" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="35" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C84" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D84" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E84" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G84" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H84" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="29" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C85" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D85" s="30" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E85" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G85" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H85" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B86" s="35" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C86" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D86" s="36" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E86" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G86" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H86" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B87" s="29" t="inlineStr">
-        <is>
-          <t>12.10.2014</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D87" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E87" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G87" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H87" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 7  —  19.10.2014</t>
-        </is>
-      </c>
-      <c r="B88" s="27" t="n"/>
-      <c r="C88" s="27" t="n"/>
-      <c r="D88" s="27" t="n"/>
-      <c r="E88" s="27" t="n"/>
-      <c r="F88" s="27" t="n"/>
-      <c r="G88" s="27" t="n"/>
-      <c r="H88" s="27" t="n"/>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B89" s="29" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C89" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D89" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E89" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G89" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H89" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B90" s="35" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C90" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D90" s="36" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E90" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G90" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H90" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B91" s="29" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C91" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D91" s="30" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E91" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G91" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H91" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B92" s="35" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C92" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D92" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E92" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G92" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H92" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B93" s="29" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C93" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D93" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E93" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G93" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H93" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B94" s="35" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C94" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D94" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E94" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G94" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H94" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B95" s="29" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C95" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D95" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E95" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G95" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H95" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="B96" s="35" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C96" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D96" s="36" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E96" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G96" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H96" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B97" s="29" t="inlineStr">
-        <is>
-          <t>19.10.2014</t>
-        </is>
-      </c>
-      <c r="C97" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D97" s="30" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E97" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G97" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H97" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 8  —  26.10.2014</t>
-        </is>
-      </c>
-      <c r="B98" s="27" t="n"/>
-      <c r="C98" s="27" t="n"/>
-      <c r="D98" s="27" t="n"/>
-      <c r="E98" s="27" t="n"/>
-      <c r="F98" s="27" t="n"/>
-      <c r="G98" s="27" t="n"/>
-      <c r="H98" s="27" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B99" s="29" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C99" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D99" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E99" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G99" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H99" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B100" s="35" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C100" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D100" s="36" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E100" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G100" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H100" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B101" s="29" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C101" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D101" s="30" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E101" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G101" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H101" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B102" s="35" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C102" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D102" s="36" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E102" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G102" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H102" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B103" s="29" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C103" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D103" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E103" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G103" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H103" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B104" s="35" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C104" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D104" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E104" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G104" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H104" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B105" s="29" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C105" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D105" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E105" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G105" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H105" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B106" s="35" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C106" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D106" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E106" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G106" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H106" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B107" s="29" t="inlineStr">
-        <is>
-          <t>26.10.2014</t>
-        </is>
-      </c>
-      <c r="C107" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D107" s="30" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="E107" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G107" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H107" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 9  —  02.11.2014</t>
-        </is>
-      </c>
-      <c r="B108" s="27" t="n"/>
-      <c r="C108" s="27" t="n"/>
-      <c r="D108" s="27" t="n"/>
-      <c r="E108" s="27" t="n"/>
-      <c r="F108" s="27" t="n"/>
-      <c r="G108" s="27" t="n"/>
-      <c r="H108" s="27" t="n"/>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B109" s="29" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C109" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D109" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E109" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="G109" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H109" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B110" s="35" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C110" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D110" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E110" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="G110" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H110" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B111" s="29" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C111" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D111" s="30" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E111" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G111" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H111" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B112" s="35" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C112" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D112" s="36" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E112" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G112" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H112" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B113" s="29" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C113" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D113" s="30" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E113" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G113" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H113" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B114" s="35" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C114" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D114" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E114" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G114" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H114" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B115" s="29" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C115" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D115" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E115" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G115" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H115" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B116" s="35" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C116" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D116" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E116" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G116" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H116" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B117" s="29" t="inlineStr">
-        <is>
-          <t>02.11.2014</t>
-        </is>
-      </c>
-      <c r="C117" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D117" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="E117" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G117" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H117" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 10  —  09.11.2014</t>
-        </is>
-      </c>
-      <c r="B118" s="27" t="n"/>
-      <c r="C118" s="27" t="n"/>
-      <c r="D118" s="27" t="n"/>
-      <c r="E118" s="27" t="n"/>
-      <c r="F118" s="27" t="n"/>
-      <c r="G118" s="27" t="n"/>
-      <c r="H118" s="27" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B119" s="29" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C119" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D119" s="30" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E119" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G119" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H119" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B120" s="35" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C120" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D120" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E120" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G120" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H120" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B121" s="29" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C121" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D121" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E121" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G121" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H121" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B122" s="35" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C122" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D122" s="36" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E122" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G122" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H122" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B123" s="29" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C123" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D123" s="30" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E123" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G123" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H123" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B124" s="35" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C124" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D124" s="36" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E124" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G124" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H124" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B125" s="29" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C125" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D125" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E125" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G125" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H125" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B126" s="35" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C126" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D126" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E126" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G126" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H126" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B127" s="29" t="inlineStr">
-        <is>
-          <t>09.11.2014</t>
-        </is>
-      </c>
-      <c r="C127" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D127" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="E127" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G127" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H127" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 11  —  16.11.2014</t>
-        </is>
-      </c>
-      <c r="B128" s="27" t="n"/>
-      <c r="C128" s="27" t="n"/>
-      <c r="D128" s="27" t="n"/>
-      <c r="E128" s="27" t="n"/>
-      <c r="F128" s="27" t="n"/>
-      <c r="G128" s="27" t="n"/>
-      <c r="H128" s="27" t="n"/>
-    </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B129" s="29" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C129" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D129" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E129" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="G129" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H129" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B130" s="35" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C130" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D130" s="36" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E130" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="G130" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H130" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B131" s="29" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C131" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D131" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E131" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G131" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H131" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B132" s="35" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C132" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D132" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E132" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G132" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H132" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B133" s="29" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C133" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D133" s="30" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E133" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G133" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H133" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B134" s="35" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C134" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D134" s="36" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E134" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G134" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H134" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B135" s="29" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C135" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D135" s="30" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E135" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G135" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H135" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B136" s="35" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C136" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D136" s="36" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E136" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G136" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H136" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B137" s="29" t="inlineStr">
-        <is>
-          <t>16.11.2014</t>
-        </is>
-      </c>
-      <c r="C137" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D137" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="E137" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G137" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H137" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 12  —  23.11.2014</t>
-        </is>
-      </c>
-      <c r="B138" s="27" t="n"/>
-      <c r="C138" s="27" t="n"/>
-      <c r="D138" s="27" t="n"/>
-      <c r="E138" s="27" t="n"/>
-      <c r="F138" s="27" t="n"/>
-      <c r="G138" s="27" t="n"/>
-      <c r="H138" s="27" t="n"/>
-    </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B139" s="29" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C139" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D139" s="30" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E139" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G139" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H139" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B140" s="35" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C140" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D140" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E140" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G140" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H140" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B141" s="29" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C141" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D141" s="30" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E141" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G141" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H141" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B142" s="35" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C142" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D142" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E142" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G142" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H142" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B143" s="29" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C143" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D143" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E143" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G143" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H143" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B144" s="35" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C144" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D144" s="36" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E144" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G144" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H144" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B145" s="29" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C145" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D145" s="30" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E145" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G145" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H145" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B146" s="35" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C146" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D146" s="36" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E146" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G146" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H146" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B147" s="29" t="inlineStr">
-        <is>
-          <t>23.11.2014</t>
-        </is>
-      </c>
-      <c r="C147" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D147" s="30" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="E147" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G147" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H147" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 13  —  30.11.2014</t>
-        </is>
-      </c>
-      <c r="B148" s="27" t="n"/>
-      <c r="C148" s="27" t="n"/>
-      <c r="D148" s="27" t="n"/>
-      <c r="E148" s="27" t="n"/>
-      <c r="F148" s="27" t="n"/>
-      <c r="G148" s="27" t="n"/>
-      <c r="H148" s="27" t="n"/>
-    </row>
-    <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B149" s="29" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C149" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D149" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E149" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="G149" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H149" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B150" s="35" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C150" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D150" s="36" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E150" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="G150" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H150" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B151" s="29" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C151" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D151" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E151" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G151" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H151" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B152" s="35" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C152" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D152" s="36" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E152" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G152" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H152" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B153" s="29" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C153" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D153" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E153" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G153" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H153" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B154" s="35" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C154" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D154" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E154" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G154" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H154" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B155" s="29" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C155" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D155" s="30" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E155" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G155" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H155" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B156" s="35" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C156" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D156" s="36" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E156" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G156" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H156" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B157" s="29" t="inlineStr">
-        <is>
-          <t>30.11.2014</t>
-        </is>
-      </c>
-      <c r="C157" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D157" s="30" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="E157" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G157" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H157" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 14  —  07.12.2014</t>
-        </is>
-      </c>
-      <c r="B158" s="27" t="n"/>
-      <c r="C158" s="27" t="n"/>
-      <c r="D158" s="27" t="n"/>
-      <c r="E158" s="27" t="n"/>
-      <c r="F158" s="27" t="n"/>
-      <c r="G158" s="27" t="n"/>
-      <c r="H158" s="27" t="n"/>
-    </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B159" s="29" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C159" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D159" s="30" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E159" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G159" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H159" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B160" s="35" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C160" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D160" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E160" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G160" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H160" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B161" s="29" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C161" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D161" s="30" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E161" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G161" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H161" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B162" s="35" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C162" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D162" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E162" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G162" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H162" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B163" s="29" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C163" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D163" s="30" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E163" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G163" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H163" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B164" s="35" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C164" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D164" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E164" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G164" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H164" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B165" s="29" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C165" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D165" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E165" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G165" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H165" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B166" s="35" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C166" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D166" s="36" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E166" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G166" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H166" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B167" s="29" t="inlineStr">
-        <is>
-          <t>07.12.2014</t>
-        </is>
-      </c>
-      <c r="C167" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D167" s="30" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="E167" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G167" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H167" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 15  —  14.12.2014</t>
-        </is>
-      </c>
-      <c r="B168" s="27" t="n"/>
-      <c r="C168" s="27" t="n"/>
-      <c r="D168" s="27" t="n"/>
-      <c r="E168" s="27" t="n"/>
-      <c r="F168" s="27" t="n"/>
-      <c r="G168" s="27" t="n"/>
-      <c r="H168" s="27" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B169" s="29" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C169" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D169" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E169" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="G169" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H169" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B170" s="35" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C170" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D170" s="36" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E170" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="G170" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H170" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B171" s="29" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C171" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D171" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E171" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G171" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H171" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B172" s="35" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C172" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D172" s="36" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E172" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G172" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H172" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B173" s="29" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C173" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D173" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E173" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G173" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H173" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B174" s="35" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C174" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D174" s="36" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E174" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G174" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H174" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B175" s="29" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C175" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D175" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E175" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G175" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H175" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="15" customHeight="1">
-      <c r="A176" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B176" s="35" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C176" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D176" s="36" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E176" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G176" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H176" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B177" s="29" t="inlineStr">
-        <is>
-          <t>14.12.2014</t>
-        </is>
-      </c>
-      <c r="C177" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D177" s="30" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="E177" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G177" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H177" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 16  —  21.12.2014</t>
-        </is>
-      </c>
-      <c r="B178" s="27" t="n"/>
-      <c r="C178" s="27" t="n"/>
-      <c r="D178" s="27" t="n"/>
-      <c r="E178" s="27" t="n"/>
-      <c r="F178" s="27" t="n"/>
-      <c r="G178" s="27" t="n"/>
-      <c r="H178" s="27" t="n"/>
-    </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B179" s="29" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C179" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D179" s="30" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E179" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="G179" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H179" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B180" s="35" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C180" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D180" s="36" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E180" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F180" s="9" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G180" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H180" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B181" s="29" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C181" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D181" s="30" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E181" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G181" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H181" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B182" s="35" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C182" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D182" s="36" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E182" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G182" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H182" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B183" s="29" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C183" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D183" s="30" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E183" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G183" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H183" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B184" s="35" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C184" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D184" s="36" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E184" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G184" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H184" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B185" s="29" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C185" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D185" s="30" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E185" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G185" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H185" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B186" s="35" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C186" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D186" s="36" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E186" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G186" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H186" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="15" customHeight="1">
-      <c r="A187" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B187" s="29" t="inlineStr">
-        <is>
-          <t>21.12.2014</t>
-        </is>
-      </c>
-      <c r="C187" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D187" s="30" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="E187" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G187" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H187" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="26" t="inlineStr">
-        <is>
-          <t>ТУР 17  —  28.12.2014</t>
-        </is>
-      </c>
-      <c r="B188" s="27" t="n"/>
-      <c r="C188" s="27" t="n"/>
-      <c r="D188" s="27" t="n"/>
-      <c r="E188" s="27" t="n"/>
-      <c r="F188" s="27" t="n"/>
-      <c r="G188" s="27" t="n"/>
-      <c r="H188" s="27" t="n"/>
-    </row>
-    <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B189" s="29" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C189" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D189" s="30" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="E189" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="G189" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H189" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B190" s="35" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C190" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D190" s="36" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="E190" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F190" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 5</t>
-        </is>
-      </c>
-      <c r="G190" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H190" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B191" s="29" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C191" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D191" s="30" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E191" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 4</t>
-        </is>
-      </c>
-      <c r="G191" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H191" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B192" s="35" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C192" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D192" s="36" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="E192" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F192" s="9" t="inlineStr">
-        <is>
-          <t>Орлы 3</t>
-        </is>
-      </c>
-      <c r="G192" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H192" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B193" s="29" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C193" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D193" s="30" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="E193" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>Орлы 2</t>
-        </is>
-      </c>
-      <c r="G193" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H193" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B194" s="35" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C194" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D194" s="36" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="E194" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F194" s="9" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="G194" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H194" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B195" s="29" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C195" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D195" s="30" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E195" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="G195" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H195" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B196" s="35" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C196" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D196" s="36" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="E196" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="G196" s="38" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H196" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="15" customHeight="1">
-      <c r="A197" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B197" s="29" t="inlineStr">
-        <is>
-          <t>28.12.2014</t>
-        </is>
-      </c>
-      <c r="C197" s="29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D197" s="30" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="E197" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>Молот</t>
-        </is>
-      </c>
-      <c r="G197" s="32" t="inlineStr">
-        <is>
-          <t>Поле №2</t>
-        </is>
-      </c>
-      <c r="H197" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="40" t="inlineStr">
-        <is>
-          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1). Для переноса матча меняй дату/время. Распечатай: Файл → Печать → Альбомная, вписать на 1 стр.</t>
+      <c r="G103" s="53" t="inlineStr">
+        <is>
+          <t>Поле №2 (Группа C)</t>
+        </is>
+      </c>
+      <c r="H103" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="40" t="inlineStr">
+        <is>
+          <t>* В каждой группе — 3 тура, 6 матчей (один круг). Для выхода в плей-офф бери по 1-2 лучшие команды из каждой группы. Счёт вписывай в столбец «Счёт». Группу E можешь переименовать, резерв убери если не нужен.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A27:H197"/>
-  <mergeCells count="23">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A148:H148"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A138:H138"/>
+  <autoFilter ref="A36:H103"/>
+  <mergeCells count="12">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A178:H178"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="A118:H118"/>
-    <mergeCell ref="A158:H158"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A105:H105"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A188:H188"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A199:H199"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A61:H61"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Mikhail_5_Sezonov_Raspisanie.xlsx
+++ b/Mikhail_5_Sezonov_Raspisanie.xlsx
@@ -14675,12 +14675,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Тетерин</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -14725,12 +14725,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Якимов</t>
+          <t>Колюжный</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -14775,12 +14775,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
@@ -14800,12 +14800,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -14850,12 +14850,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Цыганов</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -14950,12 +14950,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Колюжный</t>
+          <t>Уразаков</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -15000,12 +15000,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Куликов</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -15025,12 +15025,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -15104,7 +15104,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>ГРУППА A — 6 команды: 68 школа, Школа 175/96, Крылья дубль-школа №7, Школа 64/92, Смена КС (К), Школа 139</t>
+          <t>ГРУППА A — 6 команды: 68 школа, Школа 64/92, Школа 16, Комета, Школа 35, Орлы 2</t>
         </is>
       </c>
     </row>
@@ -15166,12 +15166,12 @@
       </c>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="C30" s="48" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Тетерин</t>
         </is>
       </c>
       <c r="D30" s="49" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="B31" s="43" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="D31" s="45" t="inlineStr">
@@ -15216,12 +15216,12 @@
       </c>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="C32" s="48" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="D32" s="49" t="inlineStr">
@@ -15241,12 +15241,12 @@
       </c>
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>Якимов</t>
+          <t>Колюжный</t>
         </is>
       </c>
       <c r="D33" s="45" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="B34" s="47" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="C34" s="48" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D34" s="49" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="F37" s="43" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="G37" s="53" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="D38" s="56" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="E38" s="49" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="F38" s="47" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="G38" s="57" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="D39" s="52" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="E39" s="45" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="F39" s="43" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="G39" s="53" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="D40" s="56" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="E40" s="49" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D41" s="52" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="E41" s="45" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F41" s="43" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="G41" s="53" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="D42" s="56" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="F42" s="47" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="G42" s="57" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F43" s="43" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="G43" s="53" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="D44" s="56" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="E44" s="49" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="F44" s="47" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="G44" s="57" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="D45" s="52" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="E45" s="45" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="F45" s="43" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="G45" s="53" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="D46" s="56" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="E46" s="49" t="inlineStr">
@@ -15750,17 +15750,17 @@
       </c>
       <c r="D47" s="52" t="inlineStr">
         <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
           <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="E47" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="43" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="G47" s="53" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="D48" s="56" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="E48" s="49" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="F48" s="47" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="G48" s="57" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="F49" s="43" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="G49" s="53" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="D50" s="56" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="E50" s="49" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="F50" s="47" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Орлы 2</t>
         </is>
       </c>
       <c r="G50" s="57" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="D51" s="52" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="E51" s="45" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="F51" s="43" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="G51" s="53" t="inlineStr">
@@ -15937,7 +15937,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="59" t="inlineStr">
         <is>
-          <t>ГРУППА B — 6 команды: Школа 16, КС 26, Смена-Ведиси, Комета, Молот, Олимп</t>
+          <t>ГРУППА B — 6 команды: Школа 175/96, Смена КС (К), КС 26, Молот, Олимп, Орлы 3</t>
         </is>
       </c>
     </row>
@@ -15974,12 +15974,12 @@
       </c>
       <c r="B55" s="43" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="D55" s="45" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="C56" s="48" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="D56" s="49" t="inlineStr">
@@ -16024,12 +16024,12 @@
       </c>
       <c r="B57" s="43" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="C57" s="44" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="D57" s="45" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="C58" s="48" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Цыганов</t>
         </is>
       </c>
       <c r="D58" s="49" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="B59" s="43" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="C59" s="44" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="D59" s="45" t="inlineStr">
@@ -16099,12 +16099,12 @@
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="C60" s="48" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D60" s="49" t="inlineStr">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="D63" s="52" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="E63" s="45" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="F63" s="43" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="G63" s="53" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="D64" s="56" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="E64" s="49" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="F64" s="47" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="G64" s="57" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="D65" s="52" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="E65" s="45" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="F65" s="43" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="G65" s="53" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="D66" s="56" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="E66" s="49" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F66" s="47" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="G66" s="57" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="D67" s="52" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="E67" s="45" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="F67" s="43" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="G67" s="53" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="D68" s="56" t="inlineStr">
         <is>
+          <t>Смена КС (К)</t>
+        </is>
+      </c>
+      <c r="E68" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="47" t="inlineStr">
+        <is>
           <t>КС 26</t>
-        </is>
-      </c>
-      <c r="E68" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="47" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="G68" s="57" t="inlineStr">
@@ -16423,7 +16423,7 @@
       </c>
       <c r="D69" s="52" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="E69" s="45" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="F69" s="43" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="G69" s="53" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="D70" s="56" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="E70" s="49" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="F70" s="47" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="G70" s="57" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="D71" s="52" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="E71" s="45" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="F71" s="43" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="G71" s="53" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="D72" s="56" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="E72" s="49" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="F72" s="47" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="G72" s="57" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="D73" s="52" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="E73" s="45" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="F73" s="43" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="G73" s="53" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="D74" s="56" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="E74" s="49" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="F74" s="47" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="G74" s="57" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="D75" s="52" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="E75" s="45" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="F75" s="43" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="G75" s="53" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="D76" s="56" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="E76" s="49" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="F76" s="47" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Орлы 3</t>
         </is>
       </c>
       <c r="G76" s="57" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="D77" s="52" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="E77" s="45" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="F77" s="43" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="G77" s="53" t="inlineStr">
@@ -16770,7 +16770,7 @@
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="60" t="inlineStr">
         <is>
-          <t>ГРУППА C — 6 команды: Школа 35, Галатасарай, Орлы 2, Орлы 3, Орлы 4, Орлы 5</t>
+          <t>ГРУППА C — 6 команды: Крылья дубль-школа №7, Школа 139, Смена-Ведиси, Галатасарай, Орлы 4, Орлы 5</t>
         </is>
       </c>
     </row>
@@ -16807,12 +16807,12 @@
       </c>
       <c r="B81" s="43" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="C81" s="44" t="inlineStr">
         <is>
-          <t>Колюжный</t>
+          <t>Уразаков</t>
         </is>
       </c>
       <c r="D81" s="45" t="inlineStr">
@@ -16832,12 +16832,12 @@
       </c>
       <c r="B82" s="47" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="C82" s="48" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="D82" s="49" t="inlineStr">
@@ -16857,12 +16857,12 @@
       </c>
       <c r="B83" s="43" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="C83" s="44" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Куликов</t>
         </is>
       </c>
       <c r="D83" s="45" t="inlineStr">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B84" s="47" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="C84" s="48" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="D84" s="49" t="inlineStr">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="D89" s="52" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="E89" s="45" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="D90" s="56" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="E90" s="49" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="D91" s="52" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="E91" s="45" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="F91" s="43" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="G91" s="53" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="F92" s="47" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="G92" s="57" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="F93" s="43" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="G93" s="53" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="D94" s="56" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="E94" s="49" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="F94" s="47" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="G94" s="57" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="D95" s="52" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="E95" s="45" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="F95" s="43" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="G95" s="53" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="F96" s="47" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="G96" s="57" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="F97" s="43" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="G97" s="53" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="D98" s="56" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="E98" s="49" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="F98" s="47" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="G98" s="57" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="D99" s="52" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="E99" s="45" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="F99" s="43" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="G99" s="53" t="inlineStr">
@@ -17496,7 +17496,7 @@
       </c>
       <c r="D101" s="52" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="E101" s="45" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F101" s="43" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="G101" s="53" t="inlineStr">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="D102" s="56" t="inlineStr">
         <is>
-          <t>Орлы 2</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="E102" s="49" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="D103" s="52" t="inlineStr">
         <is>
-          <t>Орлы 3</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="E103" s="45" t="inlineStr">
@@ -23788,12 +23788,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Профики-2</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -23813,12 +23813,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Цыганов</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Огонь 2</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Профики-2</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Тетерин</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -23913,12 +23913,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -23938,12 +23938,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Огонь 3</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -23988,12 +23988,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -24038,12 +24038,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Барсы</t>
+          <t>Огонь 4</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -24063,12 +24063,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Красная фурия 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Касьянов</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -24088,12 +24088,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Олимп 2</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -24113,12 +24113,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Огонь 2</t>
+          <t>Барсы</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -24138,7 +24138,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Огонь 3</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -24163,12 +24163,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Огонь 4</t>
+          <t>Красная фурия 2</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Касьянов</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -24188,12 +24188,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Олимп 2</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -24267,7 +24267,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>ГРУППА A — 4 команды: Эверест 2, Школа 64/92, Школа 139, Профики</t>
+          <t>ГРУППА A — 4 команды: Эверест 2, Профики-2, Молот, Огонь 2</t>
         </is>
       </c>
     </row>
@@ -24329,12 +24329,12 @@
       </c>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Профики-2</t>
         </is>
       </c>
       <c r="C32" s="48" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="D32" s="49" t="inlineStr">
@@ -24354,12 +24354,12 @@
       </c>
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Цыганов</t>
         </is>
       </c>
       <c r="D33" s="45" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="B34" s="47" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Огонь 2</t>
         </is>
       </c>
       <c r="C34" s="48" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D34" s="49" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="F37" s="43" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Огонь 2</t>
         </is>
       </c>
       <c r="G37" s="53" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="D38" s="56" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Профики-2</t>
         </is>
       </c>
       <c r="E38" s="49" t="inlineStr">
@@ -24513,7 +24513,7 @@
       </c>
       <c r="F38" s="47" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="G38" s="57" t="inlineStr">
@@ -24543,7 +24543,7 @@
       </c>
       <c r="D39" s="52" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="E39" s="45" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="D40" s="56" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Огонь 2</t>
         </is>
       </c>
       <c r="E40" s="49" t="inlineStr">
@@ -24593,7 +24593,7 @@
       </c>
       <c r="F40" s="47" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Профики-2</t>
         </is>
       </c>
       <c r="G40" s="57" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="F41" s="43" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Профики-2</t>
         </is>
       </c>
       <c r="G41" s="53" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="D42" s="56" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="F42" s="47" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Огонь 2</t>
         </is>
       </c>
       <c r="G42" s="57" t="inlineStr">
@@ -24690,7 +24690,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="59" t="inlineStr">
         <is>
-          <t>ГРУППА B — 4 команды: Профики-2, школа 16, КС 26, Комета</t>
+          <t>ГРУППА B — 4 команды: Школа 64/92, школа 16, Школа 1, Огонь 3</t>
         </is>
       </c>
     </row>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="B46" s="43" t="inlineStr">
         <is>
-          <t>Профики-2</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="C46" s="44" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Тетерин</t>
         </is>
       </c>
       <c r="D46" s="45" t="inlineStr">
@@ -24777,12 +24777,12 @@
       </c>
       <c r="B48" s="43" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="C48" s="44" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="D48" s="45" t="inlineStr">
@@ -24802,12 +24802,12 @@
       </c>
       <c r="B49" s="47" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Огонь 3</t>
         </is>
       </c>
       <c r="C49" s="48" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D49" s="49" t="inlineStr">
@@ -24886,7 +24886,7 @@
       </c>
       <c r="D52" s="56" t="inlineStr">
         <is>
-          <t>Профики-2</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="E52" s="49" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="F52" s="47" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Огонь 3</t>
         </is>
       </c>
       <c r="G52" s="57" t="inlineStr">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="F53" s="43" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="G53" s="53" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="D54" s="56" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="E54" s="49" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="F54" s="47" t="inlineStr">
         <is>
-          <t>Профики-2</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="G54" s="57" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="D55" s="52" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Огонь 3</t>
         </is>
       </c>
       <c r="E55" s="45" t="inlineStr">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="D56" s="56" t="inlineStr">
         <is>
-          <t>Профики-2</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="E56" s="49" t="inlineStr">
@@ -25086,7 +25086,7 @@
       </c>
       <c r="D57" s="52" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="E57" s="45" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="F57" s="43" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Огонь 3</t>
         </is>
       </c>
       <c r="G57" s="53" t="inlineStr">
@@ -25113,7 +25113,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="60" t="inlineStr">
         <is>
-          <t>ГРУППА C — 4 команды: Молот, Школа 1, Школа 1/2, Барсы</t>
+          <t>ГРУППА C — 4 команды: Школа 139, КС 26, Школа 1/2, Огонь 4</t>
         </is>
       </c>
     </row>
@@ -25150,12 +25150,12 @@
       </c>
       <c r="B61" s="43" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="C61" s="44" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="D61" s="45" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="B62" s="47" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="C62" s="48" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="D62" s="49" t="inlineStr">
@@ -25225,12 +25225,12 @@
       </c>
       <c r="B64" s="47" t="inlineStr">
         <is>
-          <t>Барсы</t>
+          <t>Огонь 4</t>
         </is>
       </c>
       <c r="C64" s="48" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="D64" s="49" t="inlineStr">
@@ -25309,7 +25309,7 @@
       </c>
       <c r="D67" s="52" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="E67" s="45" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="F67" s="43" t="inlineStr">
         <is>
-          <t>Барсы</t>
+          <t>Огонь 4</t>
         </is>
       </c>
       <c r="G67" s="53" t="inlineStr">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="D68" s="56" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="E68" s="49" t="inlineStr">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="F69" s="43" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="G69" s="53" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="D70" s="56" t="inlineStr">
         <is>
-          <t>Барсы</t>
+          <t>Огонь 4</t>
         </is>
       </c>
       <c r="E70" s="49" t="inlineStr">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="F70" s="47" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="G70" s="57" t="inlineStr">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="D71" s="52" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="E71" s="45" t="inlineStr">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="F71" s="43" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="G71" s="53" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="F72" s="47" t="inlineStr">
         <is>
-          <t>Барсы</t>
+          <t>Огонь 4</t>
         </is>
       </c>
       <c r="G72" s="57" t="inlineStr">
@@ -25536,7 +25536,7 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="61" t="inlineStr">
         <is>
-          <t>ГРУППА D — 4 команды: Красная фурия 2, Олимп 2, Огонь 2, Огонь 3</t>
+          <t>ГРУППА D — 4 команды: Профики, Комета, Барсы, Огонь 5</t>
         </is>
       </c>
     </row>
@@ -25573,12 +25573,12 @@
       </c>
       <c r="B76" s="43" t="inlineStr">
         <is>
-          <t>Красная фурия 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="C76" s="44" t="inlineStr">
         <is>
-          <t>Касьянов</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="D76" s="45" t="inlineStr">
@@ -25598,12 +25598,12 @@
       </c>
       <c r="B77" s="47" t="inlineStr">
         <is>
-          <t>Олимп 2</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="C77" s="48" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="D77" s="49" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="B78" s="43" t="inlineStr">
         <is>
-          <t>Огонь 2</t>
+          <t>Барсы</t>
         </is>
       </c>
       <c r="C78" s="44" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="D78" s="45" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="B79" s="47" t="inlineStr">
         <is>
-          <t>Огонь 3</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="C79" s="48" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="D82" s="56" t="inlineStr">
         <is>
-          <t>Красная фурия 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="E82" s="49" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F82" s="47" t="inlineStr">
         <is>
-          <t>Огонь 3</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="G82" s="57" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>Олимп 2</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="E83" s="45" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="F83" s="43" t="inlineStr">
         <is>
-          <t>Огонь 2</t>
+          <t>Барсы</t>
         </is>
       </c>
       <c r="G83" s="53" t="inlineStr">
@@ -25812,7 +25812,7 @@
       </c>
       <c r="D84" s="56" t="inlineStr">
         <is>
-          <t>Огонь 2</t>
+          <t>Барсы</t>
         </is>
       </c>
       <c r="E84" s="49" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="F84" s="47" t="inlineStr">
         <is>
-          <t>Красная фурия 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="G84" s="57" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>Огонь 3</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="E85" s="45" t="inlineStr">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="F85" s="43" t="inlineStr">
         <is>
-          <t>Олимп 2</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="G85" s="53" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="D86" s="56" t="inlineStr">
         <is>
-          <t>Красная фурия 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="E86" s="49" t="inlineStr">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="F86" s="47" t="inlineStr">
         <is>
-          <t>Олимп 2</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="G86" s="57" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="D87" s="52" t="inlineStr">
         <is>
-          <t>Огонь 2</t>
+          <t>Барсы</t>
         </is>
       </c>
       <c r="E87" s="45" t="inlineStr">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="F87" s="43" t="inlineStr">
         <is>
-          <t>Огонь 3</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="G87" s="53" t="inlineStr">
@@ -25959,7 +25959,7 @@
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="62" t="inlineStr">
         <is>
-          <t>ГРУППА E — 4 команды: Огонь 4, Огонь 5, Дружба, Эверест 3 (резерв)</t>
+          <t>ГРУППА E — 4 команды: Красная фурия 2, Олимп 2, Дружба, Эверест 3 (резерв)</t>
         </is>
       </c>
     </row>
@@ -25996,12 +25996,12 @@
       </c>
       <c r="B91" s="43" t="inlineStr">
         <is>
-          <t>Огонь 4</t>
+          <t>Красная фурия 2</t>
         </is>
       </c>
       <c r="C91" s="44" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Касьянов</t>
         </is>
       </c>
       <c r="D91" s="45" t="inlineStr">
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B92" s="47" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Олимп 2</t>
         </is>
       </c>
       <c r="C92" s="48" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="D92" s="49" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="D97" s="52" t="inlineStr">
         <is>
-          <t>Огонь 4</t>
+          <t>Красная фурия 2</t>
         </is>
       </c>
       <c r="E97" s="45" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="D98" s="56" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Олимп 2</t>
         </is>
       </c>
       <c r="E98" s="49" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="F99" s="43" t="inlineStr">
         <is>
-          <t>Огонь 4</t>
+          <t>Красная фурия 2</t>
         </is>
       </c>
       <c r="G99" s="53" t="inlineStr">
@@ -26285,7 +26285,7 @@
       </c>
       <c r="F100" s="47" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Олимп 2</t>
         </is>
       </c>
       <c r="G100" s="57" t="inlineStr">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="D101" s="52" t="inlineStr">
         <is>
-          <t>Огонь 4</t>
+          <t>Красная фурия 2</t>
         </is>
       </c>
       <c r="E101" s="45" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="F101" s="43" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Олимп 2</t>
         </is>
       </c>
       <c r="G101" s="53" t="inlineStr">
